--- a/review/etnografiya/may-december/july/july.xlsx
+++ b/review/etnografiya/may-december/july/july.xlsx
@@ -108,7 +108,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему не всякой косой работают одинаково?</t>
+          <t xml:space="preserve">Изгиб косы-горбуши подсказывает движение косаря. Форма инструмента связана с работой тела, а не только с остротой металлического края.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -135,7 +135,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что меняется, если рукоять слишком длинна?</t>
+          <t xml:space="preserve">Косовище подгоняют под человека. Деревянная рукоять соединяет рост, хват и движение — удобство рождается из точного соответствия работнику.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -162,7 +162,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему работа в поле прерывается короткими остановками?</t>
+          <t xml:space="preserve">Брусок возвращает косе рабочую остроту. Покос требует заботы об инструменте: остановка для правки становится частью непрерывного труда.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как устроить жизнь, когда рабочее место далеко от дома?</t>
+          <t xml:space="preserve">На долгий покос берут больше одной косы. Еда, одежда и рабочие вещи собирают повседневную жизнь там, где семье предстоит провести несколько дней.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -216,7 +216,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему скошенную траву не сразу уносят под крышу?</t>
+          <t xml:space="preserve">Скошенная трава ещё не стала зимним запасом. Просушка требует времени и внимания — поспешность может перечеркнуть тяжёлую работу покоса.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -243,7 +243,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему у летнего дня такое имя?</t>
+          <t xml:space="preserve">Банный обычай входит в день Аграфены Купальницы. Подготовка тела и домашние действия соединяются с местным порядком летнего праздника.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -270,7 +270,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как отличить народное предание от свойства растения?</t>
+          <t xml:space="preserve">Купальский рассказ обещает чудесный цветок. Предание открывает народное воображение и ожидание необычного, сохраняя отличие от ботанического факта.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -297,7 +297,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли разобраться в большой семье по одному рассказу?</t>
+          <t xml:space="preserve">За семейным столом видна сеть родства. Один человек оказывается для соседей сыном, супругом или дядей — связь зависит от точки отсчёта.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как разместить много лёгкого, но объёмного груза?</t>
+          <t xml:space="preserve">Сено хранят над хозяйственным двором. Запас занимает верхний ярус дома и связывает устройство постройки с годовым ритмом ухода за животными.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -351,7 +351,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как несколько людей работают без одинаковых заданий?</t>
+          <t xml:space="preserve">Артель делит большое дело между людьми. Общий результат складывается из разных ролей, согласованности действий и принятого порядка работы.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -378,7 +378,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как накормить семью, когда все далеко от печи?</t>
+          <t xml:space="preserve">Полевой обед должен добраться до работников. Сосуды и переноска становятся частью питания — домашняя еда получает собственный маршрут.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -405,7 +405,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что связывает праздник и начало сенокоса в Кижах?</t>
+          <t xml:space="preserve">Петров день отмечает перемену летнего хозяйственного ритма. Праздник включён в местный год работ, который не сводится к одной общей схеме.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -432,7 +432,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему два сильных гребца могут мешать друг другу?</t>
+          <t xml:space="preserve">Два весла должны работать согласованно. Направление лодки зависит от соотношения движений — совместное усилие требует общего ритма.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -459,7 +459,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что может служить якорем без сложной металлической формы?</t>
+          <t xml:space="preserve">Тяжёлый камень удерживает лодку через привязанную снасть. Природный материал получает новое назначение в продуманном рыбацком устройстве.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как вещь из села становится музейным свидетельством?</t>
+          <t xml:space="preserve">Коллекция Ольги Семёновой начинается со встреч с людьми и вещами. За музейным собранием стоит личная работа узнавания и сохранения.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему название вещи без места и имени почти бесполезно?</t>
+          <t xml:space="preserve">Полевой блокнот удерживает то, что легко забыть после встречи. Имя, место и обстоятельства записи помогают вещи сохранить человеческий контекст.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как восстановить одну ячейку, не переделывая всё полотно?</t>
+          <t xml:space="preserve">Рыбацкая игла проводит нить через ячейки сети. Починка возвращает снасти рабочую форму — добыча начинается с терпеливого ручного ремонта.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как переносная ёмкость связана со средой рыбака?</t>
+          <t xml:space="preserve">Садок оставляет пойманную рыбу в воде. Устройство продолжает работу рыбака после ловли, удерживая улов в отдельном пространстве.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему у человека рядом с ульем появляется дым?</t>
+          <t xml:space="preserve">Дымарь входит в набор пасечника. Форма прибора и направленный выход дыма показывают, как инструмент подчинён конкретной работе с ульем.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как природная форма превращается в хозяйственную вещь?</t>
+          <t xml:space="preserve">Ствол дерева становится ульем-колодой. Человек использует природную форму, превращая её в часть устроенного пчелиного хозяйства.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что меняется, когда часть улья становится съёмной?</t>
+          <t xml:space="preserve">Рамку можно вынуть из улья отдельно. Съёмная деталь меняет доступ к внутреннему устройству — работа пасечника получает новую возможность.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как несколько слабых полос становятся одним креплением?</t>
+          <t xml:space="preserve">Тонкое лыко собирается в прочную верёвку. Скручивание связывает отдельные волокна: запас прочности рождается из их совместной работы.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Где нужна ткань, которую не наденешь на праздник?</t>
+          <t xml:space="preserve">Грубая рогожа тоже требует ткацкого умения. Польза прочного полотна держится на порядке переплетения, даже когда вещь не называют нарядной.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему деревянная вещь выглядит металлической?</t>
+          <t xml:space="preserve">Хохломская ложка сияет золотым цветом, оставаясь деревянной. Отделка меняет вид материала — мастерство скрыто под знакомым праздничным блеском.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как кисть получает свет и тень без смены краски?</t>
+          <t xml:space="preserve">Один синий цвет даёт множество оттенков гжельского мазка. Нажим и движение кисти превращают ограниченную палитру в объёмный рисунок.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему узор легко узнать издалека?</t>
+          <t xml:space="preserve">Круги и полосы становятся нарядом дымковской барышни. Простой элемент работает вместе с формой фигурки и ритмом всей росписи.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кто этот персонаж между человеком и конём?</t>
+          <t xml:space="preserve">Каргопольский Полкан соединяет необычные черты в глиняной фигуре. Местная игрушка хранит собственный образ героя, узнаваемый по силуэту.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему плоский рисунок иначе смотрится на объёме?</t>
+          <t xml:space="preserve">Цветок Полховского Майдана ложится на округлую поверхность. Роспись рассчитана на объём: рисунок продолжается за пределами одного взгляда.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как сделать так, чтобы каждая фигура вошла в следующую?</t>
+          <t xml:space="preserve">Матрёшки должны войти одна в другую. Размер каждой фигурки связан с соседними — точность токарной работы удерживает расписную семью вместе.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что гремит в игрушке, у которой ничего не видно?</t>
+          <t xml:space="preserve">Внутри берестяного шаркунка спрятан источник звука. Переплетённая оболочка превращает движение руки в слышимый ответ маленькой игрушки.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли найти ручную работу по двум похожим предметам?</t>
+          <t xml:space="preserve">Ручные вещи немного различаются даже в одном ряду. След инструмента и ладони сохраняет решения мастера, которые не повторяются совершенно одинаково.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
